--- a/src/Excelsior.Tests/PrintSetupTests.Print.verified.xlsx
+++ b/src/Excelsior.Tests/PrintSetupTests.Print.verified.xlsx
@@ -247,7 +247,7 @@
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." prompt="Required field" sqref="A2:A5">
       <formula1>ISNUMBER(A2)</formula1>
     </dataValidation>
@@ -256,6 +256,10 @@
     </dataValidation>
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="C2:C5">
       <formula1>LEN(TRIM(C2))&gt;0</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="D2:D5">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
     </dataValidation>
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number." sqref="E2:E5">
       <formula1>ISNUMBER(E2)</formula1>
